--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487635_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487635_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>8.343999999999999</v>
+        <v>7.1705</v>
       </c>
       <c r="E2" t="n">
-        <v>7.3352</v>
+        <v>6.4343</v>
       </c>
       <c r="F2" t="n">
-        <v>1.0087</v>
+        <v>0.7362</v>
       </c>
       <c r="G2" t="n">
         <v>5.2466</v>
@@ -610,13 +610,13 @@
         <v>1.7463</v>
       </c>
       <c r="S2" t="n">
-        <v>1.7093</v>
+        <v>0.5358000000000001</v>
       </c>
       <c r="T2" t="n">
-        <v>1.2752</v>
+        <v>0.3743</v>
       </c>
       <c r="U2" t="n">
-        <v>0.4341</v>
+        <v>0.1615</v>
       </c>
       <c r="V2" t="n">
         <v>0.6119</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>6.6994</v>
+        <v>6.9085</v>
       </c>
       <c r="E3" t="n">
-        <v>5.4552</v>
+        <v>5.5553</v>
       </c>
       <c r="F3" t="n">
-        <v>1.2442</v>
+        <v>1.3532</v>
       </c>
       <c r="G3" t="n">
         <v>6.0842</v>
@@ -688,13 +688,13 @@
         <v>1.7463</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.3401</v>
+        <v>-0.1309</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.12</v>
+        <v>-0.0199</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.22</v>
+        <v>-0.111</v>
       </c>
       <c r="V3" t="n">
         <v>1.1493</v>
@@ -721,10 +721,10 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.1046</v>
+        <v>4.0045</v>
       </c>
       <c r="E4" t="n">
-        <v>2.0527</v>
+        <v>1.9526</v>
       </c>
       <c r="F4" t="n">
         <v>2.0519</v>
@@ -766,10 +766,10 @@
         <v>1.9403</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.3398</v>
+        <v>-0.4399</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.1806</v>
+        <v>-0.2807</v>
       </c>
       <c r="U4" t="n">
         <v>-0.1592</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.6993</v>
+        <v>2.1353</v>
       </c>
       <c r="E5" t="n">
-        <v>2.1224</v>
+        <v>1.722</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5768</v>
+        <v>0.4133</v>
       </c>
       <c r="G5" t="n">
         <v>1.705</v>
@@ -844,13 +844,13 @@
         <v>1.3582</v>
       </c>
       <c r="S5" t="n">
-        <v>0.9823</v>
+        <v>0.4183</v>
       </c>
       <c r="T5" t="n">
-        <v>0.8501</v>
+        <v>0.4497</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1321</v>
+        <v>-0.0314</v>
       </c>
       <c r="V5" t="n">
         <v>-1.3463</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.1505</v>
+        <v>0.423</v>
       </c>
       <c r="E6" t="n">
         <v>-0.5489000000000001</v>
       </c>
       <c r="F6" t="n">
-        <v>0.6993</v>
+        <v>0.9719</v>
       </c>
       <c r="G6" t="n">
         <v>0.06610000000000001</v>
@@ -922,13 +922,13 @@
         <v>1.3582</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.5574</v>
+        <v>-0.2849</v>
       </c>
       <c r="T6" t="n">
         <v>0.0617</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.6191</v>
+        <v>-0.3465</v>
       </c>
       <c r="V6" t="n">
         <v>1.2239</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>P. ARGÜELLES ELORZA</t>
+          <t>A. SISTAC RODRIGUEZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.3094</v>
+        <v>0.123</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.4342</v>
+        <v>-1.1746</v>
       </c>
       <c r="F7" t="n">
-        <v>2.1248</v>
+        <v>1.2976</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.5056</v>
+        <v>-0.6521</v>
       </c>
       <c r="H7" t="n">
-        <v>1.7622</v>
+        <v>-1.6848</v>
       </c>
       <c r="I7" t="n">
-        <v>-2.2679</v>
+        <v>1.0327</v>
       </c>
       <c r="J7" t="n">
-        <v>-1.5718</v>
+        <v>-0.01</v>
       </c>
       <c r="K7" t="n">
-        <v>0.2678</v>
+        <v>-1.8825</v>
       </c>
       <c r="L7" t="n">
-        <v>-1.8396</v>
+        <v>1.8725</v>
       </c>
       <c r="M7" t="n">
-        <v>1.0662</v>
+        <v>-0.6421</v>
       </c>
       <c r="N7" t="n">
-        <v>1.4945</v>
+        <v>0.1977</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.4282</v>
+        <v>-0.8398</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>1.7463</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.9403</v>
+        <v>-0.9702</v>
       </c>
       <c r="R7" t="n">
-        <v>1.9403</v>
+        <v>2.7164</v>
       </c>
       <c r="S7" t="n">
-        <v>0.4783</v>
+        <v>-1.3652</v>
       </c>
       <c r="T7" t="n">
-        <v>0.1839</v>
+        <v>-0.7108</v>
       </c>
       <c r="U7" t="n">
-        <v>0.2944</v>
+        <v>-0.6544</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.2821</v>
+        <v>0.394</v>
       </c>
       <c r="W7" t="n">
-        <v>0.894</v>
+        <v>0.5164</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.1761</v>
+        <v>-0.1224</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. SISTAC RODRIGUEZ</t>
+          <t>P. ARGÜELLES ELORZA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.4593</v>
+        <v>-0.4913</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.6751</v>
+        <v>-2.5343</v>
       </c>
       <c r="F8" t="n">
-        <v>1.2158</v>
+        <v>2.043</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.6521</v>
+        <v>-0.5056</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.6848</v>
+        <v>1.7622</v>
       </c>
       <c r="I8" t="n">
-        <v>1.0327</v>
+        <v>-2.2679</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.01</v>
+        <v>-1.5718</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.8825</v>
+        <v>0.2678</v>
       </c>
       <c r="L8" t="n">
-        <v>1.8725</v>
+        <v>-1.8396</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.6421</v>
+        <v>1.0662</v>
       </c>
       <c r="N8" t="n">
-        <v>0.1977</v>
+        <v>1.4945</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.8398</v>
+        <v>-0.4282</v>
       </c>
       <c r="P8" t="n">
-        <v>1.7463</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.9702</v>
+        <v>-1.9403</v>
       </c>
       <c r="R8" t="n">
-        <v>2.7164</v>
+        <v>1.9403</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.9475</v>
+        <v>0.2964</v>
       </c>
       <c r="T8" t="n">
-        <v>-1.2113</v>
+        <v>0.0838</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.7362</v>
+        <v>0.2126</v>
       </c>
       <c r="V8" t="n">
-        <v>0.394</v>
+        <v>-0.2821</v>
       </c>
       <c r="W8" t="n">
-        <v>0.5164</v>
+        <v>0.894</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.1224</v>
+        <v>-1.1761</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.0888</v>
+        <v>-2.1884</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.5527</v>
+        <v>-1.3525</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.5361</v>
+        <v>-0.8359</v>
       </c>
       <c r="G10" t="n">
         <v>-2.2067</v>
@@ -1234,13 +1234,13 @@
         <v>1.3582</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.2985</v>
+        <v>-0.3981</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.1806</v>
+        <v>0.0196</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.1179</v>
+        <v>-0.4177</v>
       </c>
       <c r="V10" t="n">
         <v>-0.9418</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-5.3482</v>
+        <v>-5.3026</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.0211</v>
+        <v>-3.921</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.3271</v>
+        <v>-1.3816</v>
       </c>
       <c r="G11" t="n">
         <v>-0.0603</v>
@@ -1312,13 +1312,13 @@
         <v>0.5821</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.6431</v>
+        <v>-0.5975</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.2423</v>
+        <v>-0.1422</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.4008</v>
+        <v>-0.4553</v>
       </c>
       <c r="V11" t="n">
         <v>-1.3463</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-7.1974</v>
+        <v>-6.1879</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.2957</v>
+        <v>-3.6951</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.9017</v>
+        <v>-2.4928</v>
       </c>
       <c r="G12" t="n">
         <v>-3.4889</v>
@@ -1390,13 +1390,13 @@
         <v>1.7463</v>
       </c>
       <c r="S12" t="n">
-        <v>-2.2622</v>
+        <v>-1.2528</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.9691</v>
+        <v>-0.3685</v>
       </c>
       <c r="U12" t="n">
-        <v>-1.2931</v>
+        <v>-0.8843</v>
       </c>
       <c r="V12" t="n">
         <v>-0.2821</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>5.370799999999999</v>
+        <v>5.3707</v>
       </c>
       <c r="E13" t="n">
-        <v>2.437799999999998</v>
+        <v>2.437799999999999</v>
       </c>
       <c r="F13" t="n">
-        <v>2.9327</v>
+        <v>2.932900000000001</v>
       </c>
       <c r="G13" t="n">
         <v>6.065600000000001</v>
@@ -1447,7 +1447,7 @@
         <v>4.5232</v>
       </c>
       <c r="L13" t="n">
-        <v>2.864300000000001</v>
+        <v>2.8643</v>
       </c>
       <c r="M13" t="n">
         <v>-1.3219</v>
@@ -1468,10 +1468,10 @@
         <v>16.4926</v>
       </c>
       <c r="S13" t="n">
-        <v>-3.2187</v>
+        <v>-3.2188</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.5330000000000001</v>
+        <v>-0.5329999999999999</v>
       </c>
       <c r="U13" t="n">
         <v>-2.6857</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>6.0344</v>
+        <v>4.9422</v>
       </c>
       <c r="E14" t="n">
-        <v>5.0577</v>
+        <v>3.8565</v>
       </c>
       <c r="F14" t="n">
-        <v>0.9767</v>
+        <v>1.0857</v>
       </c>
       <c r="G14" t="n">
         <v>2.4438</v>
@@ -1546,13 +1546,13 @@
         <v>0.7761</v>
       </c>
       <c r="S14" t="n">
-        <v>1.6384</v>
+        <v>0.5462</v>
       </c>
       <c r="T14" t="n">
-        <v>1.9661</v>
+        <v>0.7649</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.3277</v>
+        <v>-0.2187</v>
       </c>
       <c r="V14" t="n">
         <v>1.1761</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.1881</v>
+        <v>4.5519</v>
       </c>
       <c r="E15" t="n">
-        <v>4.0982</v>
+        <v>4.2984</v>
       </c>
       <c r="F15" t="n">
-        <v>0.08989999999999999</v>
+        <v>0.2535</v>
       </c>
       <c r="G15" t="n">
         <v>4.12</v>
@@ -1624,13 +1624,13 @@
         <v>1.1642</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.3755</v>
+        <v>-0.0118</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.4229</v>
+        <v>-0.2227</v>
       </c>
       <c r="U15" t="n">
-        <v>0.0474</v>
+        <v>0.2109</v>
       </c>
       <c r="V15" t="n">
         <v>0.4436</v>
@@ -1657,10 +1657,10 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.5589</v>
+        <v>3.2586</v>
       </c>
       <c r="E16" t="n">
-        <v>2.2151</v>
+        <v>1.9148</v>
       </c>
       <c r="F16" t="n">
         <v>1.3438</v>
@@ -1702,10 +1702,10 @@
         <v>2.3284</v>
       </c>
       <c r="S16" t="n">
-        <v>0.7772</v>
+        <v>0.4769</v>
       </c>
       <c r="T16" t="n">
-        <v>0.6695</v>
+        <v>0.3692</v>
       </c>
       <c r="U16" t="n">
         <v>0.1077</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.3401</v>
+        <v>1.2489</v>
       </c>
       <c r="E17" t="n">
-        <v>0.1373</v>
+        <v>-0.0629</v>
       </c>
       <c r="F17" t="n">
-        <v>1.2027</v>
+        <v>1.3118</v>
       </c>
       <c r="G17" t="n">
         <v>-1.2438</v>
@@ -1780,13 +1780,13 @@
         <v>1.7463</v>
       </c>
       <c r="S17" t="n">
-        <v>0.8376</v>
+        <v>0.7464</v>
       </c>
       <c r="T17" t="n">
-        <v>0.9959</v>
+        <v>0.7957</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.1584</v>
+        <v>-0.0493</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>S. RODRIGUEZ GREGORIO</t>
+          <t>F. SANTAMARIA LEON</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.4274</v>
+        <v>-0.7368</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.6651</v>
+        <v>-0.1279</v>
       </c>
       <c r="F18" t="n">
-        <v>0.2378</v>
+        <v>-0.6089</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.6696</v>
+        <v>0.3932</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.0406</v>
+        <v>-0.5355</v>
       </c>
       <c r="I18" t="n">
-        <v>0.3709</v>
+        <v>0.9287</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.2063</v>
+        <v>0.7955</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.8609</v>
+        <v>-0.0165</v>
       </c>
       <c r="L18" t="n">
-        <v>0.6546</v>
+        <v>0.8119</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.4633</v>
+        <v>-0.4023</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.1796</v>
+        <v>-0.5191</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.2836</v>
+        <v>0.1168</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.7761</v>
+        <v>0.7761</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.9403</v>
+        <v>-0.194</v>
       </c>
       <c r="R18" t="n">
-        <v>1.1642</v>
+        <v>0.9702</v>
       </c>
       <c r="S18" t="n">
-        <v>2.1285</v>
+        <v>-0.6822</v>
       </c>
       <c r="T18" t="n">
-        <v>1.4816</v>
+        <v>-0.7292999999999999</v>
       </c>
       <c r="U18" t="n">
-        <v>0.647</v>
+        <v>0.0471</v>
       </c>
       <c r="V18" t="n">
-        <v>-1.1101</v>
+        <v>-1.2239</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.1101</v>
+        <v>-1.2239</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>F. SANTAMARIA LEON</t>
+          <t>S. RODRIGUEZ GREGORIO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.819</v>
+        <v>-1.0275</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.4282</v>
+        <v>-0.9654</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.3908</v>
+        <v>-0.062</v>
       </c>
       <c r="G19" t="n">
-        <v>0.3932</v>
+        <v>-0.6696</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.5355</v>
+        <v>-1.0406</v>
       </c>
       <c r="I19" t="n">
-        <v>0.9287</v>
+        <v>0.3709</v>
       </c>
       <c r="J19" t="n">
-        <v>0.7955</v>
+        <v>-0.2063</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.0165</v>
+        <v>-0.8609</v>
       </c>
       <c r="L19" t="n">
-        <v>0.8119</v>
+        <v>0.6546</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.4023</v>
+        <v>-0.4633</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.5191</v>
+        <v>-0.1796</v>
       </c>
       <c r="O19" t="n">
-        <v>0.1168</v>
+        <v>-0.2836</v>
       </c>
       <c r="P19" t="n">
-        <v>0.7761</v>
+        <v>-0.7761</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.194</v>
+        <v>-1.9403</v>
       </c>
       <c r="R19" t="n">
-        <v>0.9702</v>
+        <v>1.1642</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.7645</v>
+        <v>1.5284</v>
       </c>
       <c r="T19" t="n">
-        <v>-1.0296</v>
+        <v>1.1813</v>
       </c>
       <c r="U19" t="n">
-        <v>0.2652</v>
+        <v>0.3472</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.2239</v>
+        <v>-1.1101</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.2239</v>
+        <v>-1.1101</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.4435</v>
+        <v>-1.6709</v>
       </c>
       <c r="E20" t="n">
-        <v>0.3575</v>
+        <v>0.1573</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.801</v>
+        <v>-1.8283</v>
       </c>
       <c r="G20" t="n">
         <v>-0.9034</v>
@@ -2014,13 +2014,13 @@
         <v>2.3284</v>
       </c>
       <c r="S20" t="n">
-        <v>0.6256</v>
+        <v>0.3981</v>
       </c>
       <c r="T20" t="n">
-        <v>0.9365</v>
+        <v>0.7363</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.3109</v>
+        <v>-0.3381</v>
       </c>
       <c r="V20" t="n">
         <v>-1.5537</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.4943</v>
+        <v>-2.4021</v>
       </c>
       <c r="E21" t="n">
-        <v>-4.209</v>
+        <v>-3.0078</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7148</v>
+        <v>0.6057</v>
       </c>
       <c r="G21" t="n">
         <v>-1.9712</v>
@@ -2092,13 +2092,13 @@
         <v>1.7463</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.2308</v>
+        <v>0.8614000000000001</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.7020999999999999</v>
+        <v>0.4991</v>
       </c>
       <c r="U21" t="n">
-        <v>0.4713</v>
+        <v>0.3623</v>
       </c>
       <c r="V21" t="n">
         <v>0.066</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-5.2565</v>
+        <v>-5.4116</v>
       </c>
       <c r="E22" t="n">
-        <v>-4.9046</v>
+        <v>-5.305</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.352</v>
+        <v>-0.1067</v>
       </c>
       <c r="G22" t="n">
         <v>-2.3069</v>
@@ -2170,13 +2170,13 @@
         <v>1.5523</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.2111</v>
+        <v>-0.3662</v>
       </c>
       <c r="T22" t="n">
-        <v>0.1233</v>
+        <v>-0.2771</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.3344</v>
+        <v>-0.0891</v>
       </c>
       <c r="V22" t="n">
         <v>-0.2161</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-9.051600000000001</v>
+        <v>-8.1234</v>
       </c>
       <c r="E23" t="n">
-        <v>-4.5919</v>
+        <v>-3.691</v>
       </c>
       <c r="F23" t="n">
-        <v>-4.4596</v>
+        <v>-4.4324</v>
       </c>
       <c r="G23" t="n">
         <v>-3.0677</v>
@@ -2248,13 +2248,13 @@
         <v>1.7463</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.2066</v>
+        <v>-0.2784</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.3325</v>
+        <v>-0.4316</v>
       </c>
       <c r="U23" t="n">
-        <v>0.1259</v>
+        <v>0.1531</v>
       </c>
       <c r="V23" t="n">
         <v>-3.4191</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-5.3708</v>
+        <v>-5.370700000000001</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.933000000000002</v>
+        <v>-2.933</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.4377</v>
+        <v>-2.4378</v>
       </c>
       <c r="G24" t="n">
         <v>-6.0657</v>
@@ -2332,7 +2332,7 @@
         <v>2.6858</v>
       </c>
       <c r="U24" t="n">
-        <v>0.5331000000000001</v>
+        <v>0.5330999999999999</v>
       </c>
       <c r="V24" t="n">
         <v>-1.5536</v>
